--- a/Result/profitability/5344.xlsx
+++ b/Result/profitability/5344.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.29</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01875</v>
+        <v>0.004999999999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>16.27</v>
+        <v>15.0075</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06875000000000001</v>
+        <v>0.05875</v>
       </c>
       <c r="N3" t="n">
-        <v>21.13625</v>
+        <v>20.7425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0975</v>
+        <v>0.115</v>
       </c>
       <c r="N4" t="n">
-        <v>24.5075</v>
+        <v>26.18875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1625</v>
+        <v>0.1875</v>
       </c>
       <c r="N5" t="n">
-        <v>31.71375</v>
+        <v>32.075</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.235</v>
+        <v>0.24875</v>
       </c>
       <c r="N6" t="n">
-        <v>37.17875</v>
+        <v>38.67</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.53</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3125</v>
+        <v>0.315</v>
       </c>
       <c r="N7" t="n">
-        <v>44.3375</v>
+        <v>44.77625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1394,7 +1394,7 @@
         <v>0.3375</v>
       </c>
       <c r="N8" t="n">
-        <v>48.2675</v>
+        <v>48.36375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9832,6 +9832,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5344</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>95</v>
+      </c>
+      <c r="D75" t="n">
+        <v>82</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.8475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7699999999999996</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06164931945556451</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.111111111111111</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.890000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.278688524590164</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
